--- a/docs/Login-Instruktur-UNTAR.xlsx
+++ b/docs/Login-Instruktur-UNTAR.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login UNTAR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Untar Kampus 2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Login UNTAR'!$1:$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,41 +26,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="004E5A53"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="008C3A28"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="001B2620"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001D3A2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="000369A1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,17 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D3A2D"/>
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C5141"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F0E9"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,50 +101,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B9B5A5"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00B9B5A5"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00B9B5A5"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B9B5A5"/>
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,248 +522,277 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Login Instruktur — Daily Dose Untar Kampus 2</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Portal: v2.dailydosepilates.com/sign-in  ·  Sumber: Master Instruktur Juni 2026  ·  Instruktur lintas-cabang memakai 1 username tanpa kode cabang.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Password awal sama untuk semua (12345678). Minta instruktur menggantinya saat login pertama; centang kolom terakhir bila sudah.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+          <t>Portal Login: https://v2.dailydosepilates.com/sign-in  ·  Login bisa menggunakan Username / Email / No. HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Password awal semua instruktur: 12345678. Mohon segera ganti password saat login pertama kali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Nama Instruktur</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Cabang Kerja</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Cabang</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Username</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Password Awal</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Sudah Ganti Password</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Status Login</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Fendy</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>GG, UNTAR</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>fendy</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Indah</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>UNTAR</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>indahUNTAR</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Lina</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>MK, UNTAR</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>linaMKUNTAR</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Listy</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>UNTAR</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>listyUNTAR</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Naokki</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNTAR</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>naokkiUNTAR</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Vania</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>UNTAR</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>vaniaUNTAR</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Vinny</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>UNTAR</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>vinnyUNTAR</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>12345678</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>SUKSES</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
